--- a/timeline/data.xlsx
+++ b/timeline/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\郁敏\web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yumin\web\timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -90,7 +90,7 @@
     <t>image</t>
   </si>
   <si>
-    <t>images/0th.png</t>
+    <t>images/0th.webp</t>
   </si>
   <si>
     <t>0th Live 主视图</t>
@@ -114,13 +114,13 @@
     <t>「破坏一切」</t>
   </si>
   <si>
-    <t>images/1st live logo.png</t>
+    <t>images/1st live logo.webp</t>
   </si>
   <si>
     <t>1st Live Logo</t>
   </si>
   <si>
-    <t>images/1st live kv.jpg</t>
+    <t>images/1st live kv.webp</t>
   </si>
   <si>
     <t>1st Live 主视图</t>
@@ -141,7 +141,7 @@
     <t>single</t>
   </si>
   <si>
-    <t>images/黑色生日.png</t>
+    <t>images/黑色生日.webp</t>
   </si>
   <si>
     <t>黑色生日Cover</t>
@@ -162,7 +162,7 @@
     <t>「双月~Deep Into The Forest~」</t>
   </si>
   <si>
-    <t>images/双月.png</t>
+    <t>images/双月.webp</t>
   </si>
   <si>
     <t>双月Cover</t>
@@ -183,7 +183,7 @@
     <t>「Choir 'S' Choir」</t>
   </si>
   <si>
-    <t>images/CSC.png</t>
+    <t>images/CSC.webp</t>
   </si>
   <si>
     <t>CSC Cover</t>
@@ -204,7 +204,7 @@
     <t>「神明，笨蛋」</t>
   </si>
   <si>
-    <t>images/神蠢.png</t>
+    <t>images/神蠢.webp</t>
   </si>
   <si>
     <t>神明，笨蛋Cover</t>
@@ -225,7 +225,7 @@
     <t>「Mas?uerade Rhapsody Re?uest」</t>
   </si>
   <si>
-    <t>images/MRR.png</t>
+    <t>images/MRR.webp</t>
   </si>
   <si>
     <t>MRR Cover</t>
@@ -249,13 +249,13 @@
     <t>album</t>
   </si>
   <si>
-    <t>images/骰子限定.jpg</t>
+    <t>images/骰子限定.webp</t>
   </si>
   <si>
     <t>骰子专 Cover 限定</t>
   </si>
   <si>
-    <t>images/骰子通常.jpg</t>
+    <t>images/骰子通常.webp</t>
   </si>
   <si>
     <t>骰子专 Cover 通常</t>
@@ -282,10 +282,10 @@
     <t>private</t>
   </si>
   <si>
-    <t>images/20230826-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20230826-2.jpg</t>
+    <t>images/20230826-1.webp</t>
+  </si>
+  <si>
+    <t>images/20230826-2.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1695354653582746087
@@ -304,25 +304,25 @@
     <t>首次有记载的外出游玩</t>
   </si>
   <si>
-    <t>images/20230927-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-4.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-5.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-6.jpg</t>
-  </si>
-  <si>
-    <t>images/20230927-7.jpg</t>
+    <t>images/20230927-1.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-2.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-3.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-4.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-5.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-6.webp</t>
+  </si>
+  <si>
+    <t>images/20230927-7.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1706878641228190181
@@ -335,28 +335,28 @@
     <t>弄李与米泽茜一起喝万圣节下午茶</t>
   </si>
   <si>
-    <t>images/20231031-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-4.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-5.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-6.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-7.jpg</t>
-  </si>
-  <si>
-    <t>images/20231031-8.jpg</t>
+    <t>images/20231031-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-3.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-4.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-5.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-6.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-7.webp</t>
+  </si>
+  <si>
+    <t>images/20231031-8.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1719212653686788414
@@ -378,16 +378,16 @@
     <t>Cos初祥约会</t>
   </si>
   <si>
-    <t>images/20231106-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231106-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231106-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20231106-4.jpg</t>
+    <t>images/20231106-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231106-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231106-3.webp</t>
+  </si>
+  <si>
+    <t>images/20231106-4.webp</t>
   </si>
   <si>
     <t>https://x.com/sasakirico/status/1721524275415232783
@@ -407,7 +407,7 @@
 愿你度过美好的一年( ˘͈ ᵕ ˘͈  )✨</t>
   </si>
   <si>
-    <t>images/20231110.jpg</t>
+    <t>images/20231110.webp</t>
   </si>
   <si>
     <t>https://x.com/sasakirico/status/1722630161089355896</t>
@@ -422,16 +422,16 @@
     <t>私下庆生，天文馆情侣座事件，初祥桥打卡</t>
   </si>
   <si>
-    <t>images/20231120-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231120-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231120-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20231120-4.jpg</t>
+    <t>images/20231120-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231120-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231120-3.webp</t>
+  </si>
+  <si>
+    <t>images/20231120-4.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1726525962450563173</t>
@@ -446,7 +446,7 @@
     <t>佐佐木李子赠送给高尾奏音白色马尔济斯图案的家居服</t>
   </si>
   <si>
-    <t>images/20231127.jpg</t>
+    <t>images/20231127.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1729060860918964345</t>
@@ -462,13 +462,13 @@
 奏音→李子：佐佐木李子…拥有丰沛的才华与温暖的人格。华美的歌声与平日可爱的言辞之间的反差绝妙无比。内心深藏的热忱与对周围人的温柔，打动了所有人的心。</t>
   </si>
   <si>
-    <t>images/20231222-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231222-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231222-3.jpg</t>
+    <t>images/20231222-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231222-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231222-3.webp</t>
   </si>
   <si>
     <t>https://x.com/Kanon_Takao/status/1738033106849038614
@@ -484,16 +484,16 @@
     <t>玩水活动，全员在李子家聚会</t>
   </si>
   <si>
-    <t>images/20231227-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231227-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231227-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20231227-4.jpg</t>
+    <t>images/20231227-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231227-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231227-3.webp</t>
+  </si>
+  <si>
+    <t>images/20231227-4.webp</t>
   </si>
   <si>
     <t>2023/12/31</t>
@@ -505,22 +505,22 @@
     <t>结束全员行程后，两人进行了夜游，工厂游轮约会</t>
   </si>
   <si>
-    <t>images/20231231-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20231231-2.jpg</t>
-  </si>
-  <si>
-    <t>images/20231231-3.jpg</t>
-  </si>
-  <si>
-    <t>images/20231231-4.jpg</t>
-  </si>
-  <si>
-    <t>images/20231231-5.jpg</t>
-  </si>
-  <si>
-    <t>images/20231231-6.jpg</t>
+    <t>images/20231231-1.webp</t>
+  </si>
+  <si>
+    <t>images/20231231-2.webp</t>
+  </si>
+  <si>
+    <t>images/20231231-3.webp</t>
+  </si>
+  <si>
+    <t>images/20231231-4.webp</t>
+  </si>
+  <si>
+    <t>images/20231231-5.webp</t>
+  </si>
+  <si>
+    <t>images/20231231-6.webp</t>
   </si>
   <si>
     <t>https://x.com/sasakirico/status/1741337107363438613
@@ -575,10 +575,10 @@
     <t>疑似活动内容为观看宝冢DVD</t>
   </si>
   <si>
-    <t>images/20240110-1.jpg</t>
-  </si>
-  <si>
-    <t>images/20240110-2.jpg</t>
+    <t>images/20240110-1.webp</t>
+  </si>
+  <si>
+    <t>images/20240110-2.webp</t>
   </si>
   <si>
     <t>https://x.com/sasakirico/status/1744941998145249437
@@ -591,7 +591,7 @@
     <t>「美好的世界，但是并不存在」</t>
   </si>
   <si>
-    <t>images/utopia.jpg</t>
+    <t>images/utopia.webp</t>
   </si>
   <si>
     <t>Utopia Cover</t>
@@ -609,7 +609,7 @@
     <t>「Angles」</t>
   </si>
   <si>
-    <t>images/angles.jpg</t>
+    <t>images/angles.webp</t>
   </si>
   <si>
     <t>Angles Cover</t>
@@ -624,13 +624,13 @@
     <t>Ave Mujica 1st Single 「素晴らしき世界 でも どこにもない場所」发售</t>
   </si>
   <si>
-    <t>images/1st single限定.jpg</t>
+    <t>images/1st single限定.webp</t>
   </si>
   <si>
     <t>1st Single Cover 限定</t>
   </si>
   <si>
-    <t>images/1st single通常.jpg</t>
+    <t>images/1st single通常.webp</t>
   </si>
   <si>
     <t>1st Single Cover 通常</t>
@@ -648,13 +648,13 @@
     <t>「寻找着光」</t>
   </si>
   <si>
-    <t>images/2nd live logo.jpg</t>
+    <t>images/2nd live logo.webp</t>
   </si>
   <si>
     <t>2nd Live Logo</t>
   </si>
   <si>
-    <t>images/2nd live kv.jpg</t>
+    <t>images/2nd live kv.webp</t>
   </si>
   <si>
     <t>2nd Live 主视图</t>
@@ -669,7 +669,7 @@
     <t>「寻找着光」 本次演出无影像资源</t>
   </si>
   <si>
-    <t>images/2nd live 爱知.jpg</t>
+    <t>images/2nd live 爱知.webp</t>
   </si>
   <si>
     <t>2nd Live 爱知</t>
@@ -681,13 +681,13 @@
     <t>「真实」</t>
   </si>
   <si>
-    <t>images/3rd live logo.png</t>
+    <t>images/3rd live logo.webp</t>
   </si>
   <si>
     <t>3rd Live Logo</t>
   </si>
   <si>
-    <t>images/3rd live kv.jpg</t>
+    <t>images/3rd live kv.webp</t>
   </si>
   <si>
     <t>3rd Live 主视图</t>
@@ -702,7 +702,7 @@
     <t>fes</t>
   </si>
   <si>
-    <t>images/megavagas2024.jpg</t>
+    <t>images/megavagas2024.webp</t>
   </si>
   <si>
     <t>MEGA VEGAS 2024</t>
@@ -714,7 +714,7 @@
     <t>首次海外演唱会 官方精选切片「Ave Mujica」</t>
   </si>
   <si>
-    <t>images/bml2024.png</t>
+    <t>images/bml2024.webp</t>
   </si>
   <si>
     <t>BML 2024</t>
@@ -735,7 +735,7 @@
     <t>首次出演ASL</t>
   </si>
   <si>
-    <t>images/asl2024.jpg</t>
+    <t>images/asl2024.webp</t>
   </si>
   <si>
     <t>ASL 2024</t>
@@ -753,7 +753,7 @@
     <t>bandori_fes</t>
   </si>
   <si>
-    <t>images/farbe.jpg</t>
+    <t>images/farbe.webp</t>
   </si>
   <si>
     <t>Roselia「Farbe」</t>
@@ -768,7 +768,7 @@
     <t>「元素：火」</t>
   </si>
   <si>
-    <t>images/fire.jpg</t>
+    <t>images/fire.webp</t>
   </si>
   <si>
     <t>Fire Cover</t>
@@ -786,7 +786,7 @@
     <t>「元素：气」</t>
   </si>
   <si>
-    <t>images/air.png</t>
+    <t>images/air.webp</t>
   </si>
   <si>
     <t>Air Cover</t>
@@ -804,7 +804,7 @@
     <t>「元素：水」</t>
   </si>
   <si>
-    <t>images/water.png</t>
+    <t>images/water.webp</t>
   </si>
   <si>
     <t>Water Cover</t>
@@ -822,7 +822,7 @@
     <t>「元素：土」</t>
   </si>
   <si>
-    <t>images/earth.png</t>
+    <t>images/earth.webp</t>
   </si>
   <si>
     <t>Earth Cover</t>
@@ -840,7 +840,7 @@
     <t>「以太」</t>
   </si>
   <si>
-    <t>images/ether.png</t>
+    <t>images/ether.webp</t>
   </si>
   <si>
     <t>Ether Cover</t>
@@ -858,25 +858,25 @@
     <t>「元素」</t>
   </si>
   <si>
-    <t>images/元素专特装.jpg</t>
+    <t>images/元素专特装.webp</t>
   </si>
   <si>
     <t>元素专 Cover 特装</t>
   </si>
   <si>
-    <t>images/元素专特装BD.jpg</t>
+    <t>images/元素专特装BD.webp</t>
   </si>
   <si>
     <t>元素专 特装Box</t>
   </si>
   <si>
-    <t>images/元素专限定.jpg</t>
+    <t>images/元素专限定.webp</t>
   </si>
   <si>
     <t>元素专 Cover 限定</t>
   </si>
   <si>
-    <t>images/元素专通常.jpg</t>
+    <t>images/元素专通常.webp</t>
   </si>
   <si>
     <t>元素专 Cover 通常</t>
@@ -894,13 +894,13 @@
     <t>收录Ave Mujica的三首翻唱曲「暗黑天国」「KINGS」「堕天」</t>
   </si>
   <si>
-    <t>images/翻唱专限定.jpg</t>
+    <t>images/翻唱专限定.webp</t>
   </si>
   <si>
     <t>翻唱专 Cover 限定</t>
   </si>
   <si>
-    <t>images/翻唱专通常.jpg</t>
+    <t>images/翻唱专通常.webp</t>
   </si>
   <si>
     <t>翻唱专 Cover 通常</t>
@@ -918,7 +918,7 @@
     <t>武藏野双日 D1为Roselia的oml，D2为Ave Mujica的oml，互相作为开场嘉宾出演</t>
   </si>
   <si>
-    <t>images/roselia武藏野.jpg</t>
+    <t>images/roselia武藏野.webp</t>
   </si>
   <si>
     <t>Roselia「Stille Nacht, Rosen Nacht」</t>
@@ -930,13 +930,13 @@
     <t>「降临」</t>
   </si>
   <si>
-    <t>images/4th live logo.png</t>
+    <t>images/4th live logo.webp</t>
   </si>
   <si>
     <t>4th Live Logo</t>
   </si>
   <si>
-    <t>images/4th live kv.jpg</t>
+    <t>images/4th live kv.webp</t>
   </si>
   <si>
     <t>4th Live 主视图</t>
@@ -948,7 +948,7 @@
     <t>Ave Mujica 出演 ANIMAX MUSIX 2024 FALL</t>
   </si>
   <si>
-    <t>images/animax2024.jpeg</t>
+    <t>images/animax2024.webp</t>
   </si>
   <si>
     <t>ANIMAX 2024 FALL</t>
@@ -963,7 +963,7 @@
     <t>anime</t>
   </si>
   <si>
-    <t>images/animemujica.png</t>
+    <t>images/animemujica.webp</t>
   </si>
   <si>
     <t>动画 Logo</t>
@@ -5103,13 +5103,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" errorTitle="无效分类" error="请选择 organization 或 personal" sqref="C5 C18 C84 C87 C91 C112 C113 C114 C117 C118 C119 C120 C121 C122 C123 C124 C125 C2:C4 C6:C17 C19:C83 C85:C86 C88:C90 C92:C111 C115:C116 C126:C248">
+    <dataValidation type="list" errorTitle="无效分类" error="请选择 organization 或 personal" sqref="C2:C248">
       <formula1>"organization,personal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E5 E18 E84 E87 E91 E112 E113 E114 E117 E120 E121 E122 E123 E124 E125 E2:E4 E6:E17 E19:E83 E85:E86 E88:E90 E92:E111 E115:E116 E118:E119 E126:E1048576">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E1048576">
       <formula1>INDIRECT(C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" promptTitle="媒体类型" prompt="请选择媒体类型" sqref="F5 F18 F84 F87 F91 F112 F113 F114 F115 F116 F117 F118 F122 F123 F124 F125 F2:F4 F6:F17 F19:F83 F85:F86 F88:F90 F92:F111 F119:F121 F126:F248">
+    <dataValidation type="list" allowBlank="1" promptTitle="媒体类型" prompt="请选择媒体类型" sqref="F2:F248">
       <formula1>"image,video,link"</formula1>
     </dataValidation>
   </dataValidations>
